--- a/public/tangstash-import-template.xlsx
+++ b/public/tangstash-import-template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,15 +47,26 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="008A6D00"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="008A6D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -66,12 +77,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF7D6"/>
-        <bgColor rgb="00FFF7D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,16 +92,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -515,66 +522,74 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Required.</t>
+          <t>Required. English name.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Card Number</t>
+          <t>Original Name</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Required. e.g. OP01-025</t>
+          <t>Name in its native language (e.g. Japanese) — optional but nice to have.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Artist</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Leader / Character / Event / Stage</t>
+          <t>Illustrator credit — optional, manual only (not auto-scraped anywhere in the app).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Print Source</t>
+          <t>Card Number</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>e.g. OP01, ST05, EB02</t>
+          <t>Required. e.g. OP01-025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Rarity</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr"/>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Leader / Character / Event / Stage / Don!!</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Foil Type</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr"/>
+          <t>Print Source</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>e.g. OP01, ST05, EB02</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Rarity</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>
@@ -582,140 +597,491 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>0 or 1 — one row = one physical card (not a multi-copy counter).</t>
-        </is>
-      </c>
+          <t>Foil Type</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Purchase Price</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Leave blank for Wanted cards.</t>
+          <t>One or more of: Red, Green, Blue, Purple, Black, Yellow. Multiple = join with ' + ', e.g. "Red + Green".</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Purchase Currency</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
+          <t>Family Type</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>e.g. "Straw Hat Crew" — open-ended (not a fixed list). Multiple = join with ' + ', e.g. "Straw Hat Crew + Supernovas".</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Purchase Date</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD. Defaults to today if blank on a new row.</t>
+          <t>Open-ended. Multiple = join with ' + '.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Toretoku URL</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Exact listing URL for this specific card/variant — not a catalog search link.</t>
-        </is>
-      </c>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Yuyu-tei URL</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Exact listing URL for this specific card/variant.</t>
+          <t>0 or 1 — one row = one physical card (not a multi-copy counter).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>PriceCharting URL</t>
+          <t>Purchase Price</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Exact listing URL. Last-resort pricing source only.</t>
+          <t>Leave blank for Wanted cards.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Image Link</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Optional fallback — only used if none of the 3 URLs above are set.</t>
-        </is>
-      </c>
+          <t>Purchase Currency</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Condition Type</t>
+          <t>Purchase Date</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Singles / Slabs</t>
+          <t>YYYY-MM-DD. Defaults to today if blank on a new row.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Sub-Condition</t>
+          <t>Toretoku URL</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>e.g. Sealed, White Dot, Damaged — or a grade like PSA10 for Slabs.</t>
+          <t>Exact listing URL for this specific card/variant — not a catalog search link.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Grading Company</t>
+          <t>Yuyu-tei URL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Only for Slabs.</t>
+          <t>Exact listing URL for this specific card/variant.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>Image Link</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Optional fallback — only used if neither URL above is set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Additional Photos</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Optional — one or more extra photo links (e.g. a Slab's front + back scan). Multiple = join with ' + ', same as Color/Family Type/Collection, e.g.: https://ccg-imaging-cgc-tradingcards-production.s3.amazonaws.com/17799460-84d6-4eed-b308-97e6575c1284/CAR6142887-003_OBV.jpg + https://ccg-imaging-cgc-tradingcards-production.s3.amazonaws.com/17799460-84d6-4eed-b308-97e6575c1284/CAR6142887-003_REV.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Condition Type</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Singles / Slabs / Sealed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sub-Condition</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>e.g. Sealed, White Dot, Damaged — or a grade like PSA10 for Slabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Grading Company</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Only for Slabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
           <t>Cert Number</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Only for Slabs — builds a clickable verification link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Example row (for reference — NOT in the Cards tab, so nothing gets imported by accident):</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Listing UID</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Card Name</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Roronoa Zoro (Parallel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Original Name</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>ロロノア・ゾロ(パラレル)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Card Number</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>OP01-025</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Print Source</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>OP01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Foil Type</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Foil</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Family Type</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Straw Hat Crew</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Purchase Price</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>7580</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Purchase Currency</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Purchase Date</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Toretoku URL</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.toretoku.jp/item/details/158238</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Yuyu-tei URL</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>https://yuyu-tei.jp/sell/opc/card/op01/10033</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Image Link</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Additional Photos</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Condition Type</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Singles</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Sub-Condition</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Grading Company</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Cert Number</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>(blank)</t>
         </is>
       </c>
     </row>
@@ -730,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -753,205 +1119,161 @@
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Listing UID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Card Name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Original Name</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Card Number</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Print Source</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Rarity</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Foil Type</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>Family Type</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>Purchase Price</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Purchase Currency</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>Purchase Date</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>Toretoku URL</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Yuyu-tei URL</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
-        <is>
-          <t>PriceCharting URL</t>
-        </is>
-      </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="T1" s="8" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="U1" s="8" t="inlineStr">
+        <is>
+          <t>Additional Photos</t>
+        </is>
+      </c>
+      <c r="V1" s="8" t="inlineStr">
         <is>
           <t>Condition Type</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="W1" s="8" t="inlineStr">
         <is>
           <t>Sub-Condition</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="X1" s="8" t="inlineStr">
         <is>
           <t>Grading Company</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="Y1" s="8" t="inlineStr">
         <is>
           <t>Cert Number</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Roronoa Zoro (Parallel)</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>OP01-025</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Character</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>OP01</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>SR</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Foil</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Japanese</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="6" t="n">
-        <v>7580</v>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>JPY</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.toretoku.jp/item/details/158238</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>https://yuyu-tei.jp/sell/opc/card/op01/10033</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr"/>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>Singles</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="6" t="inlineStr"/>
-      <c r="T2" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="D3:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose one of: Leader, Character, Event, Stage" type="list">
-      <formula1>"Leader,Character,Event,Stage"</formula1>
+    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose one of: Leader, Character, Event, Stage, Don!!" type="list">
+      <formula1>"Leader,Character,Event,Stage,Don!!"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose one of: C, UC, R, SR, SEC, L, P, P-SR, SP" type="list">
-      <formula1>"C,UC,R,SR,SEC,L,P,P-SR,SP"</formula1>
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose one of: C, UC, R, SR, SEC, L, P, P-SR, SP, Don!!" type="list">
+      <formula1>"C,UC,R,SR,SEC,L,P,P-SR,SP,Don!!"</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose one of: Foil, Non-Foil, Textured Foil" type="list">
+    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose one of: Foil, Non-Foil, Textured Foil" type="list">
       <formula1>"Foil,Non-Foil,Textured Foil"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose one of: English, Japanese, Chinese" type="list">
+    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose one of: English, Japanese, Chinese" type="list">
       <formula1>"English,Japanese,Chinese"</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose one of: SGD, JPY, AUD, RMB, MYR, USD" type="list">
+    <dataValidation sqref="P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose one of: SGD, JPY, AUD, RMB, MYR, USD" type="list">
       <formula1>"SGD,JPY,AUD,RMB,MYR,USD"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q3:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose one of: Singles, Slabs" type="list">
-      <formula1>"Singles,Slabs"</formula1>
+    <dataValidation sqref="V2:V500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose one of: Singles, Slabs, Sealed" type="list">
+      <formula1>"Singles,Slabs,Sealed"</formula1>
     </dataValidation>
-    <dataValidation sqref="S3:S500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose one of: PSA, CGC, ARS" type="list">
+    <dataValidation sqref="X2:X500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose one of: PSA, CGC, ARS" type="list">
       <formula1>"PSA,CGC,ARS"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/tangstash-import-template.xlsx
+++ b/public/tangstash-import-template.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -786,285 +786,285 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Binder Placement</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Optional — "&lt;Binder Name&gt; &lt;Number&gt;" places this card automatically instead of arranging it by hand. Binders hold 9 slots per page, filled in reading order, so the Number is a running count across pages: 1-9 = Page 1 (slots 1-9), 10-18 = Page 2, and so on. Example: "Main Collection 24" = Page 3, Slot 6. "Don!! 36" = Page 4, Slot 9 — if a binder named "Don!!" doesn't exist yet, it's created automatically. Binder name matching ignores case. Leave blank to leave the card unplaced, same as today. If a slot is already taken (by another card, including another row in this same file), that row's placement is skipped rather than overwriting what's there — check the import summary for how many were skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Example row (for reference — NOT in the Cards tab, so nothing gets imported by accident):</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Listing UID</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>(blank)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Card Name</t>
+          <t>Listing UID</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Roronoa Zoro (Parallel)</t>
+          <t>(blank)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Original Name</t>
+          <t>Card Name</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>ロロノア・ゾロ(パラレル)</t>
+          <t>Roronoa Zoro (Parallel)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Artist</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr"/>
+          <t>Original Name</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>ロロノア・ゾロ(パラレル)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Card Number</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>OP01-025</t>
-        </is>
-      </c>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Card Number</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>OP01-025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Print Source</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>OP01</t>
+          <t>Character</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Rarity</t>
+          <t>Print Source</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>OP01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Foil Type</t>
+          <t>Rarity</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Foil</t>
+          <t>SR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Foil Type</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Foil</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Family Type</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Straw Hat Crew</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr"/>
+          <t>Family Type</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Straw Hat Crew</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Japanese</t>
-        </is>
-      </c>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Purchase Price</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Purchase Currency</t>
+          <t>Purchase Price</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>7580</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Purchase Date</t>
+          <t>Purchase Currency</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>JPY</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Toretoku URL</t>
+          <t>Purchase Date</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>https://www.toretoku.jp/item/details/158238</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Yuyu-tei URL</t>
+          <t>Toretoku URL</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>https://yuyu-tei.jp/sell/opc/card/op01/10033</t>
+          <t>https://www.toretoku.jp/item/details/158238</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>Yuyu-tei URL</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>https://yuyu-tei.jp/sell/opc/card/op01/10033</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>(blank)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Additional Photos</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>(blank)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Condition Type</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Singles</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Sub-Condition</t>
+          <t>Condition Type</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>Singles</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Grading Company</t>
+          <t>Sub-Condition</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -1076,10 +1076,34 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
+          <t>Grading Company</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
           <t>Cert Number</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Binder Placement</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>(blank)</t>
         </is>
@@ -1096,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1124,6 +1148,7 @@
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1250,6 +1275,11 @@
       <c r="Y1" s="8" t="inlineStr">
         <is>
           <t>Cert Number</t>
+        </is>
+      </c>
+      <c r="Z1" s="8" t="inlineStr">
+        <is>
+          <t>Binder Placement</t>
         </is>
       </c>
     </row>

--- a/public/tangstash-import-template.xlsx
+++ b/public/tangstash-import-template.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Blank = new card. Fill with an existing card's Listing UID to mass-update that row instead of creating a duplicate.</t>
+          <t>Blank = new card. Fill with an existing card's Listing UID to mass-update that row instead of creating a duplicate. To delete a listing instead, attach "del" or "delete" to the front or back of its UID (any case, with or without a dash) — e.g. "TS-A2B3C-delete" or "del-TS-A2B3C" — and leave the rest of that row blank; it's removed, not imported.</t>
         </is>
       </c>
     </row>
